--- a/Produkty/426_50052426.xlsx
+++ b/Produkty/426_50052426.xlsx
@@ -445,7 +445,7 @@
         <v/>
       </c>
       <c r="B2" t="str">
-        <v>732x70x28-426</v>
+        <v>732x70x28</v>
       </c>
       <c r="C2" t="str">
         <v>732</v>
@@ -486,7 +486,7 @@
         <v/>
       </c>
       <c r="B3" t="str">
-        <v>550x60x28-426</v>
+        <v>550x60x28</v>
       </c>
       <c r="C3" t="str">
         <v>550</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="B4" t="str">
-        <v>565x28x28-426</v>
+        <v>565x28x28</v>
       </c>
       <c r="C4" t="str">
         <v>565</v>
